--- a/ZR.Admin.WebApi/wwwroot/data.xlsx
+++ b/ZR.Admin.WebApi/wwwroot/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Mine\public\ZrAdminNet\ZR.Admin.WebApi\wwwroot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Mine\ZRAdmin\public\ZrAdminNet\ZR.Admin.WebApi\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED31845-7757-47B9-8FAF-89EBAAA0325E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA54739-0CB2-428A-9D5D-3245DC227B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="849" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="849" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="user" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="816">
   <si>
     <t>系统管理</t>
   </si>
@@ -2794,6 +2794,13 @@
   </si>
   <si>
     <t>zujian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sys.account.initPasswordModify</t>
+  </si>
+  <si>
+    <t>初始化密码是否提示修改</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3108,6 +3115,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3127,7 +3202,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -3417,12 +3492,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D00AC0F-0226-4E9A-8157-8C2F558D581D}">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="10" max="10" width="33.4140625" customWidth="1"/>
+    <col min="10" max="10" width="33.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>299</v>
       </c>
@@ -3463,7 +3538,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3492,7 +3567,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3521,7 +3596,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3560,16 +3635,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E508F4-5906-4688-BE06-7243F5B00B2A}">
   <dimension ref="A1:K50"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.25" customWidth="1"/>
-    <col min="4" max="4" width="11.4140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.08203125" customWidth="1"/>
-    <col min="10" max="10" width="12.9140625" customWidth="1"/>
-    <col min="11" max="11" width="19.08203125" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" customWidth="1"/>
+    <col min="10" max="10" width="12.88671875" customWidth="1"/>
+    <col min="11" max="11" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>491</v>
       </c>
@@ -3604,7 +3679,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3633,7 +3708,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3662,7 +3737,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3691,7 +3766,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3723,7 +3798,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3755,7 +3830,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3787,7 +3862,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3819,7 +3894,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3851,7 +3926,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3883,7 +3958,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3912,7 +3987,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3941,7 +4016,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3973,7 +4048,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4005,7 +4080,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4034,7 +4109,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4063,7 +4138,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4092,7 +4167,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4121,7 +4196,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4150,7 +4225,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4179,7 +4254,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4208,7 +4283,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4237,7 +4312,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4266,7 +4341,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4295,7 +4370,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4324,7 +4399,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4353,7 +4428,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4382,7 +4457,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4411,7 +4486,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4440,7 +4515,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4469,7 +4544,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4492,7 +4567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4515,7 +4590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4538,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4561,7 +4636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4584,7 +4659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4610,7 +4685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4636,7 +4711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4662,7 +4737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4685,7 +4760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4711,7 +4786,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4734,7 +4809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4757,7 +4832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4780,7 +4855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4803,7 +4878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4826,7 +4901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4849,7 +4924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4872,7 +4947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4895,7 +4970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4918,7 +4993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4950,9 +5025,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F8E602-C602-4DBE-8251-6DDEB8D8D144}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>502</v>
       </c>
@@ -4975,7 +5050,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4995,7 +5070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5015,7 +5090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5035,7 +5110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5055,7 +5130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5085,13 +5160,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D59B089-6BFD-4898-97D7-5E5DB5B781E2}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.08203125" customWidth="1"/>
-    <col min="4" max="4" width="13.25" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>512</v>
       </c>
@@ -5108,7 +5183,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5125,7 +5200,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5142,7 +5217,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5159,7 +5234,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -5176,7 +5251,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -5200,12 +5275,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1499BA89-84F4-45F4-9C1A-AC4400B29F1F}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.25" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>658</v>
       </c>
@@ -5213,7 +5288,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>660</v>
       </c>
@@ -5221,7 +5296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>661</v>
       </c>
@@ -5229,7 +5304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>662</v>
       </c>
@@ -5237,7 +5312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>663</v>
       </c>
@@ -5245,7 +5320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>664</v>
       </c>
@@ -5262,13 +5337,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A140A180-7D1B-4334-9A7F-5459F016CE4B}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.9140625" customWidth="1"/>
-    <col min="4" max="4" width="80.4140625" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="4" max="4" width="80.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>631</v>
       </c>
@@ -5285,7 +5360,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="121.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="121.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -5312,20 +5387,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O179"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.4140625" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="23.58203125" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="11" max="11" width="22.75" customWidth="1"/>
-    <col min="12" max="12" width="10.58203125" customWidth="1"/>
-    <col min="13" max="13" width="18.4140625" customWidth="1"/>
-    <col min="14" max="14" width="21.75" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.77734375" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" customWidth="1"/>
+    <col min="13" max="13" width="18.44140625" customWidth="1"/>
+    <col min="14" max="14" width="21.77734375" customWidth="1"/>
+    <col min="15" max="15" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>282</v>
       </c>
@@ -5372,7 +5447,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -5410,7 +5485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
         <v>2</v>
       </c>
@@ -5448,7 +5523,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -5486,7 +5561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>5</v>
       </c>
@@ -5524,7 +5599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>6</v>
       </c>
@@ -5564,7 +5639,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>7</v>
       </c>
@@ -5600,7 +5675,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>9</v>
       </c>
@@ -5638,7 +5713,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>8</v>
       </c>
@@ -5678,7 +5753,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>10</v>
       </c>
@@ -5720,7 +5795,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>11</v>
       </c>
@@ -5756,7 +5831,7 @@
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>12</v>
       </c>
@@ -5788,7 +5863,7 @@
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>504</v>
       </c>
@@ -5824,7 +5899,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>505</v>
       </c>
@@ -5858,7 +5933,7 @@
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <v>506</v>
       </c>
@@ -5891,7 +5966,7 @@
       <c r="L15" s="12"/>
       <c r="M15" s="12"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>507</v>
       </c>
@@ -5924,7 +5999,7 @@
       <c r="L16" s="12"/>
       <c r="M16" s="12"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>100</v>
       </c>
@@ -5966,7 +6041,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>101</v>
       </c>
@@ -6008,7 +6083,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>102</v>
       </c>
@@ -6050,7 +6125,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>103</v>
       </c>
@@ -6092,7 +6167,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>104</v>
       </c>
@@ -6134,7 +6209,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>105</v>
       </c>
@@ -6176,7 +6251,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>106</v>
       </c>
@@ -6216,7 +6291,7 @@
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>107</v>
       </c>
@@ -6258,7 +6333,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
         <v>108</v>
       </c>
@@ -6296,7 +6371,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>109</v>
       </c>
@@ -6338,7 +6413,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
         <v>110</v>
       </c>
@@ -6378,7 +6453,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>111</v>
       </c>
@@ -6418,7 +6493,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
         <v>112</v>
       </c>
@@ -6460,7 +6535,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
         <v>113</v>
       </c>
@@ -6502,7 +6577,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
         <v>114</v>
       </c>
@@ -6544,7 +6619,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
         <v>115</v>
       </c>
@@ -6586,7 +6661,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="12">
         <v>116</v>
       </c>
@@ -6628,7 +6703,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
         <v>117</v>
       </c>
@@ -6670,7 +6745,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="12">
         <v>118</v>
       </c>
@@ -6708,7 +6783,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
         <v>119</v>
       </c>
@@ -6750,7 +6825,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
         <v>500</v>
       </c>
@@ -6792,7 +6867,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
         <v>501</v>
       </c>
@@ -6834,7 +6909,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
         <v>502</v>
       </c>
@@ -6876,7 +6951,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
         <v>503</v>
       </c>
@@ -6910,7 +6985,7 @@
       <c r="M40" s="12"/>
       <c r="N40" s="12"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <v>1001</v>
       </c>
@@ -6944,7 +7019,7 @@
       <c r="M41" s="12"/>
       <c r="N41" s="12"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
         <v>1002</v>
       </c>
@@ -6978,7 +7053,7 @@
       <c r="M42" s="12"/>
       <c r="N42" s="12"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
         <v>1003</v>
       </c>
@@ -7012,7 +7087,7 @@
       <c r="M43" s="12"/>
       <c r="N43" s="12"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
         <v>1004</v>
       </c>
@@ -7046,7 +7121,7 @@
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <v>1005</v>
       </c>
@@ -7082,7 +7157,7 @@
       <c r="M45" s="12"/>
       <c r="N45" s="12"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <v>1006</v>
       </c>
@@ -7118,7 +7193,7 @@
       <c r="M46" s="12"/>
       <c r="N46" s="12"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
         <v>1007</v>
       </c>
@@ -7154,7 +7229,7 @@
       <c r="M47" s="12"/>
       <c r="N47" s="12"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
         <v>1008</v>
       </c>
@@ -7190,7 +7265,7 @@
       <c r="M48" s="12"/>
       <c r="N48" s="12"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <v>1009</v>
       </c>
@@ -7226,7 +7301,7 @@
       <c r="M49" s="12"/>
       <c r="N49" s="12"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
         <v>1010</v>
       </c>
@@ -7262,7 +7337,7 @@
       <c r="M50" s="12"/>
       <c r="N50" s="12"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <v>1011</v>
       </c>
@@ -7298,7 +7373,7 @@
       <c r="M51" s="12"/>
       <c r="N51" s="12"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <v>1012</v>
       </c>
@@ -7334,7 +7409,7 @@
       <c r="M52" s="12"/>
       <c r="N52" s="12"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <v>1013</v>
       </c>
@@ -7370,7 +7445,7 @@
       <c r="M53" s="12"/>
       <c r="N53" s="12"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="12">
         <v>1014</v>
       </c>
@@ -7406,7 +7481,7 @@
       <c r="M54" s="12"/>
       <c r="N54" s="12"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="12">
         <v>1015</v>
       </c>
@@ -7442,7 +7517,7 @@
       <c r="M55" s="12"/>
       <c r="N55" s="12"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
         <v>1016</v>
       </c>
@@ -7478,7 +7553,7 @@
       <c r="M56" s="12"/>
       <c r="N56" s="12"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <v>1017</v>
       </c>
@@ -7512,7 +7587,7 @@
       <c r="M57" s="12"/>
       <c r="N57" s="12"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
         <v>1018</v>
       </c>
@@ -7546,7 +7621,7 @@
       <c r="M58" s="12"/>
       <c r="N58" s="12"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="12">
         <v>1019</v>
       </c>
@@ -7580,7 +7655,7 @@
       <c r="M59" s="12"/>
       <c r="N59" s="12"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="12">
         <v>1020</v>
       </c>
@@ -7614,7 +7689,7 @@
       <c r="M60" s="12"/>
       <c r="N60" s="12"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="12">
         <v>1021</v>
       </c>
@@ -7648,7 +7723,7 @@
       <c r="M61" s="12"/>
       <c r="N61" s="12"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
         <v>1022</v>
       </c>
@@ -7682,7 +7757,7 @@
       <c r="M62" s="12"/>
       <c r="N62" s="12"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
         <v>1023</v>
       </c>
@@ -7716,7 +7791,7 @@
       <c r="M63" s="12"/>
       <c r="N63" s="12"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
         <v>1024</v>
       </c>
@@ -7750,7 +7825,7 @@
       <c r="M64" s="12"/>
       <c r="N64" s="12"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="12">
         <v>1025</v>
       </c>
@@ -7784,7 +7859,7 @@
       <c r="M65" s="12"/>
       <c r="N65" s="12"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="12">
         <v>1026</v>
       </c>
@@ -7818,7 +7893,7 @@
       <c r="M66" s="12"/>
       <c r="N66" s="12"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="12">
         <v>1027</v>
       </c>
@@ -7852,7 +7927,7 @@
       <c r="M67" s="12"/>
       <c r="N67" s="12"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="12">
         <v>1028</v>
       </c>
@@ -7886,7 +7961,7 @@
       <c r="M68" s="12"/>
       <c r="N68" s="12"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
         <v>1029</v>
       </c>
@@ -7920,7 +7995,7 @@
       <c r="M69" s="12"/>
       <c r="N69" s="12"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
         <v>1030</v>
       </c>
@@ -7954,7 +8029,7 @@
       <c r="M70" s="12"/>
       <c r="N70" s="12"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
         <v>1031</v>
       </c>
@@ -7988,7 +8063,7 @@
       <c r="M71" s="12"/>
       <c r="N71" s="12"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="12">
         <v>1032</v>
       </c>
@@ -8026,7 +8101,7 @@
       <c r="M72" s="12"/>
       <c r="N72" s="12"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="12">
         <v>1033</v>
       </c>
@@ -8062,7 +8137,7 @@
       <c r="M73" s="12"/>
       <c r="N73" s="12"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="12">
         <v>1034</v>
       </c>
@@ -8098,7 +8173,7 @@
       <c r="M74" s="12"/>
       <c r="N74" s="12"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="12">
         <v>1035</v>
       </c>
@@ -8134,7 +8209,7 @@
       <c r="M75" s="12"/>
       <c r="N75" s="12"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="12">
         <v>1036</v>
       </c>
@@ -8170,7 +8245,7 @@
       <c r="M76" s="12"/>
       <c r="N76" s="12"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="12">
         <v>1037</v>
       </c>
@@ -8206,7 +8281,7 @@
       <c r="M77" s="12"/>
       <c r="N77" s="12"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="12">
         <v>1038</v>
       </c>
@@ -8242,7 +8317,7 @@
       <c r="M78" s="12"/>
       <c r="N78" s="12"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="12">
         <v>1039</v>
       </c>
@@ -8282,7 +8357,7 @@
       <c r="M79" s="12"/>
       <c r="N79" s="12"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="12">
         <v>1040</v>
       </c>
@@ -8318,7 +8393,7 @@
       <c r="M80" s="12"/>
       <c r="N80" s="12"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="12">
         <v>1041</v>
       </c>
@@ -8354,7 +8429,7 @@
       <c r="M81" s="12"/>
       <c r="N81" s="12"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="12">
         <v>1042</v>
       </c>
@@ -8390,7 +8465,7 @@
       <c r="M82" s="12"/>
       <c r="N82" s="12"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="12">
         <v>1043</v>
       </c>
@@ -8426,7 +8501,7 @@
       <c r="M83" s="12"/>
       <c r="N83" s="12"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="12">
         <v>1044</v>
       </c>
@@ -8462,7 +8537,7 @@
       <c r="M84" s="12"/>
       <c r="N84" s="12"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="12">
         <v>1045</v>
       </c>
@@ -8498,7 +8573,7 @@
       <c r="M85" s="12"/>
       <c r="N85" s="12"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="12">
         <v>1046</v>
       </c>
@@ -8534,7 +8609,7 @@
       <c r="M86" s="12"/>
       <c r="N86" s="12"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="12">
         <v>1047</v>
       </c>
@@ -8574,7 +8649,7 @@
       <c r="M87" s="12"/>
       <c r="N87" s="12"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="12">
         <v>1049</v>
       </c>
@@ -8610,7 +8685,7 @@
       <c r="M88" s="12"/>
       <c r="N88" s="12"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="12">
         <v>1048</v>
       </c>
@@ -8644,7 +8719,7 @@
       <c r="M89" s="12"/>
       <c r="N89" s="12"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="12">
         <v>1050</v>
       </c>
@@ -8680,7 +8755,7 @@
       <c r="M90" s="12"/>
       <c r="N90" s="12"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="12">
         <v>1051</v>
       </c>
@@ -8716,7 +8791,7 @@
       <c r="M91" s="12"/>
       <c r="N91" s="12"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="12">
         <v>1052</v>
       </c>
@@ -8752,7 +8827,7 @@
       <c r="M92" s="12"/>
       <c r="N92" s="12"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="12">
         <v>1053</v>
       </c>
@@ -8788,7 +8863,7 @@
       <c r="M93" s="12"/>
       <c r="N93" s="12"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="12">
         <v>1054</v>
       </c>
@@ -8824,7 +8899,7 @@
       <c r="M94" s="12"/>
       <c r="N94" s="12"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="12">
         <v>1055</v>
       </c>
@@ -8860,7 +8935,7 @@
       <c r="M95" s="12"/>
       <c r="N95" s="12"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="12">
         <v>1060</v>
       </c>
@@ -8898,7 +8973,7 @@
       <c r="M96" s="12"/>
       <c r="N96" s="12"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="12">
         <v>1061</v>
       </c>
@@ -8934,7 +9009,7 @@
       <c r="M97" s="12"/>
       <c r="N97" s="12"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="12">
         <v>1062</v>
       </c>
@@ -8970,7 +9045,7 @@
       <c r="M98" s="12"/>
       <c r="N98" s="12"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="12">
         <v>1063</v>
       </c>
@@ -9006,7 +9081,7 @@
       <c r="M99" s="12"/>
       <c r="N99" s="12"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="12">
         <v>1064</v>
       </c>
@@ -9042,7 +9117,7 @@
       <c r="M100" s="12"/>
       <c r="N100" s="12"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="12">
         <v>1065</v>
       </c>
@@ -9078,7 +9153,7 @@
       <c r="M101" s="12"/>
       <c r="N101" s="12"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="12">
         <v>1070</v>
       </c>
@@ -9112,7 +9187,7 @@
       <c r="M102" s="12"/>
       <c r="N102" s="12"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="12">
         <v>1071</v>
       </c>
@@ -9146,7 +9221,7 @@
       <c r="M103" s="12"/>
       <c r="N103" s="12"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="12">
         <v>1072</v>
       </c>
@@ -9188,7 +9263,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="12">
         <v>1073</v>
       </c>
@@ -9224,7 +9299,7 @@
       <c r="M105" s="12"/>
       <c r="N105" s="12"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="12">
         <v>1074</v>
       </c>
@@ -9260,7 +9335,7 @@
       <c r="M106" s="12"/>
       <c r="N106" s="12"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="12">
         <v>1075</v>
       </c>
@@ -9296,7 +9371,7 @@
       <c r="M107" s="12"/>
       <c r="N107" s="12"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="12">
         <v>1076</v>
       </c>
@@ -9332,7 +9407,7 @@
       <c r="M108" s="12"/>
       <c r="N108" s="12"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="12">
         <v>1077</v>
       </c>
@@ -9368,7 +9443,7 @@
       <c r="M109" s="12"/>
       <c r="N109" s="12"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="12">
         <v>1078</v>
       </c>
@@ -9410,7 +9485,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="12">
         <v>1079</v>
       </c>
@@ -9446,7 +9521,7 @@
       <c r="M111" s="12"/>
       <c r="N111" s="12"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="12">
         <v>1080</v>
       </c>
@@ -9482,7 +9557,7 @@
       <c r="M112" s="12"/>
       <c r="N112" s="12"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="12">
         <v>1081</v>
       </c>
@@ -9518,7 +9593,7 @@
       <c r="M113" s="12"/>
       <c r="N113" s="12"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="12">
         <v>1082</v>
       </c>
@@ -9554,7 +9629,7 @@
       <c r="M114" s="12"/>
       <c r="N114" s="12"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="12">
         <v>1090</v>
       </c>
@@ -9590,7 +9665,7 @@
       <c r="M115" s="12"/>
       <c r="N115" s="12"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="12">
         <v>1083</v>
       </c>
@@ -9626,7 +9701,7 @@
       <c r="M116" s="12"/>
       <c r="N116" s="12"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="14">
         <v>1084</v>
       </c>
@@ -9668,7 +9743,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="14">
         <v>1085</v>
       </c>
@@ -9704,7 +9779,7 @@
       <c r="M118" s="14"/>
       <c r="N118" s="12"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="14">
         <v>1086</v>
       </c>
@@ -9740,7 +9815,7 @@
       <c r="M119" s="14"/>
       <c r="N119" s="12"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="14">
         <v>1087</v>
       </c>
@@ -9776,7 +9851,7 @@
       <c r="M120" s="14"/>
       <c r="N120" s="12"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="14">
         <v>1088</v>
       </c>
@@ -9812,7 +9887,7 @@
       <c r="M121" s="14"/>
       <c r="N121" s="12"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="14">
         <v>1089</v>
       </c>
@@ -9848,7 +9923,7 @@
       <c r="M122" s="14"/>
       <c r="N122" s="12"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="12">
         <v>1092</v>
       </c>
@@ -9884,7 +9959,7 @@
       </c>
       <c r="N123" s="12"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="12">
         <v>1091</v>
       </c>
@@ -9920,7 +9995,7 @@
       </c>
       <c r="N124" s="12"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="12">
         <v>1102</v>
       </c>
@@ -9956,7 +10031,7 @@
       </c>
       <c r="N125" s="12"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="12">
         <v>1103</v>
       </c>
@@ -9992,7 +10067,7 @@
       </c>
       <c r="N126" s="12"/>
     </row>
-    <row r="127" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="15">
         <v>1104</v>
       </c>
@@ -10034,7 +10109,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="15">
         <v>1105</v>
       </c>
@@ -10068,7 +10143,7 @@
       <c r="M128" s="15"/>
       <c r="N128" s="12"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="15">
         <v>1106</v>
       </c>
@@ -10102,7 +10177,7 @@
       <c r="M129" s="15"/>
       <c r="N129" s="12"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="15">
         <v>1107</v>
       </c>
@@ -10136,7 +10211,7 @@
       <c r="M130" s="15"/>
       <c r="N130" s="12"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="16">
         <v>1108</v>
       </c>
@@ -10178,7 +10253,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="16">
         <v>1109</v>
       </c>
@@ -10212,7 +10287,7 @@
       <c r="M132" s="16"/>
       <c r="N132" s="12"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="16">
         <v>1110</v>
       </c>
@@ -10246,7 +10321,7 @@
       <c r="M133" s="16"/>
       <c r="N133" s="12"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="14">
         <v>1111</v>
       </c>
@@ -10290,7 +10365,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="14">
         <v>1112</v>
       </c>
@@ -10324,7 +10399,7 @@
       <c r="M135" s="14"/>
       <c r="N135" s="12"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="14">
         <v>1113</v>
       </c>
@@ -10358,7 +10433,7 @@
       <c r="M136" s="14"/>
       <c r="N136" s="12"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="17">
         <v>1114</v>
       </c>
@@ -10400,7 +10475,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="17">
         <v>1115</v>
       </c>
@@ -10434,7 +10509,7 @@
       <c r="M138" s="17"/>
       <c r="N138" s="12"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="17">
         <v>1116</v>
       </c>
@@ -10468,7 +10543,7 @@
       <c r="M139" s="17"/>
       <c r="N139" s="12"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="14">
         <v>1093</v>
       </c>
@@ -10508,7 +10583,7 @@
       <c r="M140" s="12"/>
       <c r="N140" s="12"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" s="14">
         <v>1094</v>
       </c>
@@ -10544,7 +10619,7 @@
       <c r="M141" s="12"/>
       <c r="N141" s="12"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="14">
         <v>1095</v>
       </c>
@@ -10580,7 +10655,7 @@
       <c r="M142" s="12"/>
       <c r="N142" s="12"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="14">
         <v>1096</v>
       </c>
@@ -10616,7 +10691,7 @@
       <c r="M143" s="12"/>
       <c r="N143" s="12"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="14">
         <v>1097</v>
       </c>
@@ -10652,7 +10727,7 @@
       <c r="M144" s="12"/>
       <c r="N144" s="12"/>
     </row>
-    <row r="145" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="14">
         <v>1098</v>
       </c>
@@ -10688,7 +10763,7 @@
       <c r="M145" s="12"/>
       <c r="N145" s="12"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="18">
         <v>1117</v>
       </c>
@@ -10728,7 +10803,7 @@
       <c r="M146" s="12"/>
       <c r="N146" s="12"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="18">
         <v>1118</v>
       </c>
@@ -10764,7 +10839,7 @@
       <c r="M147" s="12"/>
       <c r="N147" s="12"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="18">
         <v>1119</v>
       </c>
@@ -10800,7 +10875,7 @@
       <c r="M148" s="12"/>
       <c r="N148" s="12"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="18">
         <v>1120</v>
       </c>
@@ -10836,7 +10911,7 @@
       <c r="M149" s="12"/>
       <c r="N149" s="12"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="18">
         <v>1121</v>
       </c>
@@ -10872,7 +10947,7 @@
       <c r="M150" s="12"/>
       <c r="N150" s="12"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="18">
         <v>1122</v>
       </c>
@@ -10908,7 +10983,7 @@
       <c r="M151" s="12"/>
       <c r="N151" s="12"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="20">
         <v>1123</v>
       </c>
@@ -10948,7 +11023,7 @@
       <c r="M152" s="12"/>
       <c r="N152" s="12"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="20">
         <v>1124</v>
       </c>
@@ -10980,7 +11055,7 @@
       </c>
       <c r="L153" s="20"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="20">
         <v>1125</v>
       </c>
@@ -11012,7 +11087,7 @@
       </c>
       <c r="L154" s="20"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="20">
         <v>1126</v>
       </c>
@@ -11044,7 +11119,7 @@
       </c>
       <c r="L155" s="20"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="20">
         <v>1127</v>
       </c>
@@ -11076,7 +11151,7 @@
       </c>
       <c r="L156" s="20"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="20">
         <v>1142</v>
       </c>
@@ -11110,7 +11185,7 @@
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="14">
         <v>120</v>
       </c>
@@ -11148,7 +11223,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="14">
         <v>121</v>
       </c>
@@ -11180,7 +11255,7 @@
       </c>
       <c r="L159" s="14"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="14">
         <v>122</v>
       </c>
@@ -11212,7 +11287,7 @@
       </c>
       <c r="L160" s="14"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="14">
         <v>123</v>
       </c>
@@ -11244,7 +11319,7 @@
       </c>
       <c r="L161" s="14"/>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="14">
         <v>124</v>
       </c>
@@ -11276,7 +11351,7 @@
       </c>
       <c r="L162" s="14"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="21">
         <v>1133</v>
       </c>
@@ -11314,7 +11389,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="21">
         <v>1134</v>
       </c>
@@ -11346,7 +11421,7 @@
       </c>
       <c r="L164" s="21"/>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="21">
         <v>1135</v>
       </c>
@@ -11378,7 +11453,7 @@
       </c>
       <c r="L165" s="21"/>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="21">
         <v>1136</v>
       </c>
@@ -11410,7 +11485,7 @@
       </c>
       <c r="L166" s="21"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="21">
         <v>1137</v>
       </c>
@@ -11442,7 +11517,7 @@
       </c>
       <c r="L167" s="21"/>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="14">
         <v>1138</v>
       </c>
@@ -11480,7 +11555,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="14">
         <v>1139</v>
       </c>
@@ -11516,7 +11591,7 @@
       </c>
       <c r="L169" s="14"/>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="14">
         <v>1140</v>
       </c>
@@ -11548,7 +11623,7 @@
       </c>
       <c r="L170" s="14"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="14">
         <v>1141</v>
       </c>
@@ -11580,7 +11655,7 @@
       </c>
       <c r="L171" s="14"/>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="14">
         <v>1143</v>
       </c>
@@ -11612,7 +11687,7 @@
       </c>
       <c r="L172" s="14"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="14">
         <v>1144</v>
       </c>
@@ -11644,7 +11719,7 @@
       </c>
       <c r="L173" s="14"/>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="14">
         <v>1145</v>
       </c>
@@ -11676,7 +11751,7 @@
       </c>
       <c r="L174" s="14"/>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" s="14">
         <v>1146</v>
       </c>
@@ -11714,7 +11789,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" s="20">
         <v>125</v>
       </c>
@@ -11753,7 +11828,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="20">
         <v>126</v>
       </c>
@@ -11783,7 +11858,7 @@
       </c>
       <c r="L177" s="20"/>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="20">
         <v>127</v>
       </c>
@@ -11813,7 +11888,7 @@
       </c>
       <c r="L178" s="20"/>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="20">
         <v>128</v>
       </c>
@@ -11884,14 +11959,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4172CB-C633-40F1-9E06-DA7BE35E7941}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="6" max="6" width="13.4140625" customWidth="1"/>
-    <col min="7" max="7" width="15.4140625" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>314</v>
       </c>
@@ -11923,7 +11998,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -11955,7 +12030,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -11987,7 +12062,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -12029,9 +12104,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{337D2D18-B37B-4DF5-9944-49704E9D0445}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>366</v>
       </c>
@@ -12042,7 +12117,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -12050,7 +12125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -12058,7 +12133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -12066,7 +12141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -12074,7 +12149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -12082,7 +12157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -12090,7 +12165,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
@@ -12098,7 +12173,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2</v>
       </c>
@@ -12106,7 +12181,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2</v>
       </c>
@@ -12114,7 +12189,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
@@ -12122,7 +12197,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
@@ -12130,7 +12205,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
@@ -12138,7 +12213,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -12146,7 +12221,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -12154,7 +12229,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3</v>
       </c>
@@ -12162,7 +12237,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
@@ -12170,7 +12245,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -12178,7 +12253,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2</v>
       </c>
@@ -12186,7 +12261,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2</v>
       </c>
@@ -12194,7 +12269,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2</v>
       </c>
@@ -12202,7 +12277,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2</v>
       </c>
@@ -12210,7 +12285,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2</v>
       </c>
@@ -12218,7 +12293,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2</v>
       </c>
@@ -12226,7 +12301,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2</v>
       </c>
@@ -12234,7 +12309,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2</v>
       </c>
@@ -12242,7 +12317,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2</v>
       </c>
@@ -12250,7 +12325,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>3</v>
       </c>
@@ -12261,7 +12336,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>3</v>
       </c>
@@ -12272,7 +12347,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3</v>
       </c>
@@ -12283,7 +12358,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>3</v>
       </c>
@@ -12294,7 +12369,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>3</v>
       </c>
@@ -12305,7 +12380,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>3</v>
       </c>
@@ -12316,7 +12391,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>3</v>
       </c>
@@ -12327,7 +12402,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>3</v>
       </c>
@@ -12338,7 +12413,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>3</v>
       </c>
@@ -12349,7 +12424,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>3</v>
       </c>
@@ -12360,7 +12435,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>3</v>
       </c>
@@ -12371,7 +12446,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>3</v>
       </c>
@@ -12393,17 +12468,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA152B8-C1FA-4646-A501-2C7774BC6ACC}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.33203125" customWidth="1"/>
-    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.58203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="11.4140625" customWidth="1"/>
-    <col min="6" max="6" width="83.75" customWidth="1"/>
+    <col min="3" max="3" width="27.88671875" customWidth="1"/>
+    <col min="4" max="4" width="35.5546875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
+    <col min="6" max="6" width="83.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>330</v>
       </c>
@@ -12423,7 +12498,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -12443,7 +12518,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4</v>
       </c>
@@ -12463,7 +12538,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>6</v>
       </c>
@@ -12483,7 +12558,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>8</v>
       </c>
@@ -12503,7 +12578,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9</v>
       </c>
@@ -12521,6 +12596,20 @@
       </c>
       <c r="F6" t="s">
         <v>674</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>814</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>490</v>
+      </c>
+      <c r="F7" t="s">
+        <v>815</v>
       </c>
     </row>
   </sheetData>
@@ -12532,9 +12621,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFFA53F-160B-48BA-80B0-079F0EA2A7A7}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>365</v>
       </c>
@@ -12542,7 +12631,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -12550,7 +12639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -12558,7 +12647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -12575,18 +12664,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2040177-E526-42D3-A91B-661E4F43E409}">
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.4140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.58203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.75" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" customWidth="1"/>
     <col min="17" max="17" width="15.6640625" customWidth="1"/>
     <col min="18" max="18" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>373</v>
       </c>
@@ -12639,7 +12728,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>374</v>
       </c>
@@ -12689,12 +12778,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9C4135-AFDC-4222-9830-710D942A3AED}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>361</v>
       </c>
@@ -12711,7 +12800,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -12728,7 +12817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -12745,7 +12834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -12762,7 +12851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -12779,7 +12868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -12796,7 +12885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -12813,7 +12902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -12830,7 +12919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -12847,7 +12936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -12864,7 +12953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -12881,7 +12970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -12898,7 +12987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -12915,7 +13004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -12941,16 +13030,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DA66D3-8315-4018-BF52-5D786631F136}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="19.25" customWidth="1"/>
-    <col min="4" max="5" width="8.9140625" style="3"/>
-    <col min="6" max="6" width="17.58203125" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="4" max="5" width="8.88671875" style="3"/>
+    <col min="6" max="6" width="17.5546875" customWidth="1"/>
     <col min="7" max="7" width="70.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>485</v>
       </c>
@@ -12973,7 +13062,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -12993,7 +13082,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -13013,7 +13102,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -13033,7 +13122,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -13053,7 +13142,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -13073,7 +13162,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -13093,7 +13182,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -13113,7 +13202,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -13133,7 +13222,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -13153,7 +13242,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -13173,7 +13262,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -13190,7 +13279,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -13210,7 +13299,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -13230,7 +13319,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -13253,7 +13342,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -13273,7 +13362,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -13290,7 +13379,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -13307,7 +13396,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -13327,7 +13416,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>

--- a/ZR.Admin.WebApi/wwwroot/data.xlsx
+++ b/ZR.Admin.WebApi/wwwroot/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Mine\ZRAdmin\public\ZrAdminNet\ZR.Admin.WebApi\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA54739-0CB2-428A-9D5D-3245DC227B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E873AE01-F10A-4CF2-B1A2-8F8804A50585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="849" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="818">
   <si>
     <t>系统管理</t>
   </si>
@@ -2800,7 +2800,16 @@
     <t>sys.account.initPasswordModify</t>
   </si>
   <si>
-    <t>初始化密码是否提示修改</t>
+    <t>初始化密码是否提示修改1、提醒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">密码更新周期（填写数字，数据初始化值为0不限制，若修改必须为大于0小于365的正整数），如果超过这个周期登录系统时，则在登录时就会提醒修改密码对话框');
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sys.account.passwordExpireDay</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2947,7 +2956,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -2988,6 +2997,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -12468,7 +12480,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA152B8-C1FA-4646-A501-2C7774BC6ACC}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.33203125" customWidth="1"/>
@@ -12610,6 +12622,20 @@
       </c>
       <c r="F7" t="s">
         <v>815</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>817</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>490</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>816</v>
       </c>
     </row>
   </sheetData>
